--- a/Metrics Calculator.xlsx
+++ b/Metrics Calculator.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Experiment\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{81C89688-227B-4405-8BF7-41353D1B203B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{81EA2452-C484-4C86-8A2F-F56885E9073B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="6" xr2:uid="{A8A5934F-0248-4D7D-8E3D-4BC53B41A58A}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{A8A5934F-0248-4D7D-8E3D-4BC53B41A58A}"/>
   </bookViews>
   <sheets>
     <sheet name="Sample" sheetId="1" r:id="rId1"/>
@@ -776,30 +776,31 @@
       </c>
       <c r="B2" s="7">
         <f>H2/(H2+I2)</f>
-        <v>0.68235294117647061</v>
+        <v>0.18367346938775511</v>
       </c>
       <c r="C2" s="7">
         <f>H2/(H2+J2)</f>
-        <v>0.96666666666666667</v>
+        <v>0.9</v>
       </c>
       <c r="D2" s="8">
         <f>((B2*C2)/(B2+C2))*2</f>
-        <v>0.80000000000000016</v>
+        <v>0.30508474576271183</v>
       </c>
       <c r="E2" s="9">
-        <v>60</v>
+        <v>10</v>
       </c>
       <c r="G2" s="1" t="s">
         <v>1</v>
       </c>
       <c r="H2" s="23">
-        <v>58</v>
+        <v>9</v>
       </c>
       <c r="I2" s="23">
-        <v>27</v>
+        <v>40</v>
       </c>
       <c r="J2" s="23">
-        <v>2</v>
+        <f>10-H2</f>
+        <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.2">
@@ -808,30 +809,30 @@
       </c>
       <c r="B3" s="7">
         <f>H3/(H3+I3)</f>
-        <v>0.68333333333333335</v>
+        <v>0</v>
       </c>
       <c r="C3" s="7">
         <f t="shared" ref="C3:C13" si="0">H3/(H3+J3)</f>
-        <v>0.68333333333333335</v>
+        <v>0</v>
       </c>
       <c r="D3" s="8">
-        <f t="shared" ref="D3:D13" si="1">((B3*C3)/(B3+C3))*2</f>
-        <v>0.68333333333333335</v>
+        <v>0</v>
       </c>
       <c r="E3" s="9">
-        <v>60</v>
+        <v>10</v>
       </c>
       <c r="G3" s="1" t="s">
         <v>2</v>
       </c>
       <c r="H3" s="23">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="I3" s="23">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="J3" s="23">
-        <v>19</v>
+        <f t="shared" ref="J3:J13" si="1">10-H3</f>
+        <v>10</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.2">
@@ -840,30 +841,30 @@
       </c>
       <c r="B4" s="7">
         <f t="shared" ref="B4:B13" si="2">H4/(H4+I4)</f>
-        <v>0.80821917808219179</v>
+        <v>0</v>
       </c>
       <c r="C4" s="7">
         <f t="shared" si="0"/>
-        <v>0.98333333333333328</v>
+        <v>0</v>
       </c>
       <c r="D4" s="8">
-        <f t="shared" si="1"/>
-        <v>0.88721804511278191</v>
+        <v>0</v>
       </c>
       <c r="E4" s="9">
-        <v>60</v>
+        <v>10</v>
       </c>
       <c r="G4" s="1" t="s">
         <v>3</v>
       </c>
       <c r="H4" s="23">
-        <v>59</v>
+        <v>0</v>
       </c>
       <c r="I4" s="23">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="J4" s="23">
-        <v>1</v>
+        <f t="shared" si="1"/>
+        <v>10</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.2">
@@ -872,30 +873,31 @@
       </c>
       <c r="B5" s="7">
         <f t="shared" si="2"/>
-        <v>0.65555555555555556</v>
+        <v>1</v>
       </c>
       <c r="C5" s="7">
         <f t="shared" si="0"/>
-        <v>0.98333333333333328</v>
+        <v>1</v>
       </c>
       <c r="D5" s="8">
-        <f t="shared" si="1"/>
-        <v>0.78666666666666663</v>
+        <f t="shared" ref="D3:D13" si="3">((B5*C5)/(B5+C5))*2</f>
+        <v>1</v>
       </c>
       <c r="E5" s="9">
-        <v>60</v>
+        <v>10</v>
       </c>
       <c r="G5" s="1" t="s">
         <v>5</v>
       </c>
       <c r="H5" s="23">
-        <v>59</v>
+        <v>10</v>
       </c>
       <c r="I5" s="23">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="J5" s="23">
-        <v>1</v>
+        <f t="shared" si="1"/>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.2">
@@ -904,30 +906,31 @@
       </c>
       <c r="B6" s="7">
         <f t="shared" si="2"/>
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="C6" s="7">
         <f t="shared" si="0"/>
-        <v>0.73333333333333328</v>
+        <v>0.5</v>
       </c>
       <c r="D6" s="8">
-        <f t="shared" si="1"/>
-        <v>0.76521739130434785</v>
+        <f t="shared" si="3"/>
+        <v>0.66666666666666663</v>
       </c>
       <c r="E6" s="9">
-        <v>60</v>
+        <v>10</v>
       </c>
       <c r="G6" s="1" t="s">
         <v>6</v>
       </c>
       <c r="H6" s="23">
-        <v>44</v>
+        <v>5</v>
       </c>
       <c r="I6" s="23">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="J6" s="23">
-        <v>16</v>
+        <f t="shared" si="1"/>
+        <v>5</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.2">
@@ -936,30 +939,31 @@
       </c>
       <c r="B7" s="7">
         <f t="shared" si="2"/>
-        <v>0.8571428571428571</v>
+        <v>0.38461538461538464</v>
       </c>
       <c r="C7" s="7">
         <f t="shared" si="0"/>
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="D7" s="8">
-        <f t="shared" si="1"/>
-        <v>0.70588235294117641</v>
+        <f t="shared" si="3"/>
+        <v>0.55555555555555558</v>
       </c>
       <c r="E7" s="9">
-        <v>60</v>
+        <v>10</v>
       </c>
       <c r="G7" s="1" t="s">
         <v>4</v>
       </c>
       <c r="H7" s="23">
-        <v>36</v>
+        <v>10</v>
       </c>
       <c r="I7" s="23">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="J7" s="23">
-        <v>24</v>
+        <f t="shared" si="1"/>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.2">
@@ -968,30 +972,31 @@
       </c>
       <c r="B8" s="7">
         <f t="shared" si="2"/>
-        <v>0.92452830188679247</v>
+        <v>0.8</v>
       </c>
       <c r="C8" s="7">
         <f t="shared" si="0"/>
-        <v>0.81666666666666665</v>
+        <v>0.8</v>
       </c>
       <c r="D8" s="8">
-        <f t="shared" si="1"/>
-        <v>0.86725663716814161</v>
+        <f t="shared" si="3"/>
+        <v>0.80000000000000016</v>
       </c>
       <c r="E8" s="9">
-        <v>60</v>
+        <v>10</v>
       </c>
       <c r="G8" s="1" t="s">
         <v>7</v>
       </c>
       <c r="H8" s="23">
-        <v>49</v>
+        <v>8</v>
       </c>
       <c r="I8" s="23">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J8" s="23">
-        <v>11</v>
+        <f t="shared" si="1"/>
+        <v>2</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.2">
@@ -1000,30 +1005,31 @@
       </c>
       <c r="B9" s="7">
         <f t="shared" si="2"/>
-        <v>1</v>
+        <v>0.45454545454545453</v>
       </c>
       <c r="C9" s="7">
         <f t="shared" si="0"/>
-        <v>0.66666666666666663</v>
+        <v>0.5</v>
       </c>
       <c r="D9" s="8">
-        <f t="shared" si="1"/>
-        <v>0.8</v>
+        <f t="shared" si="3"/>
+        <v>0.47619047619047616</v>
       </c>
       <c r="E9" s="9">
-        <v>60</v>
+        <v>10</v>
       </c>
       <c r="G9" s="1" t="s">
         <v>8</v>
       </c>
       <c r="H9" s="23">
-        <v>40</v>
+        <v>5</v>
       </c>
       <c r="I9" s="23">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="J9" s="23">
-        <v>20</v>
+        <f t="shared" si="1"/>
+        <v>5</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.2">
@@ -1032,30 +1038,30 @@
       </c>
       <c r="B10" s="7">
         <f t="shared" si="2"/>
-        <v>0.92307692307692313</v>
+        <v>0</v>
       </c>
       <c r="C10" s="7">
         <f t="shared" si="0"/>
-        <v>0.6</v>
-      </c>
-      <c r="D10" s="8">
-        <f t="shared" si="1"/>
-        <v>0.7272727272727274</v>
+        <v>0</v>
+      </c>
+      <c r="D10" s="11">
+        <v>0</v>
       </c>
       <c r="E10" s="9">
-        <v>60</v>
+        <v>10</v>
       </c>
       <c r="G10" s="1" t="s">
         <v>9</v>
       </c>
       <c r="H10" s="23">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="I10" s="23">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J10" s="23">
-        <v>24</v>
+        <f t="shared" si="1"/>
+        <v>10</v>
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.2">
@@ -1064,30 +1070,30 @@
       </c>
       <c r="B11" s="7">
         <f t="shared" si="2"/>
-        <v>0.96153846153846156</v>
+        <v>0</v>
       </c>
       <c r="C11" s="7">
         <f t="shared" si="0"/>
-        <v>0.41666666666666669</v>
-      </c>
-      <c r="D11" s="8">
-        <f t="shared" si="1"/>
-        <v>0.58139534883720934</v>
+        <v>0</v>
+      </c>
+      <c r="D11" s="11">
+        <v>0</v>
       </c>
       <c r="E11" s="9">
-        <v>60</v>
+        <v>10</v>
       </c>
       <c r="G11" s="1" t="s">
         <v>10</v>
       </c>
       <c r="H11" s="23">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="I11" s="23">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J11" s="23">
-        <v>35</v>
+        <f t="shared" si="1"/>
+        <v>10</v>
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.2">
@@ -1096,30 +1102,30 @@
       </c>
       <c r="B12" s="7">
         <f t="shared" si="2"/>
-        <v>0.84848484848484851</v>
+        <v>0</v>
       </c>
       <c r="C12" s="7">
         <f t="shared" si="0"/>
-        <v>0.93333333333333335</v>
-      </c>
-      <c r="D12" s="8">
-        <f t="shared" si="1"/>
-        <v>0.88888888888888895</v>
+        <v>0</v>
+      </c>
+      <c r="D12" s="11">
+        <v>0</v>
       </c>
       <c r="E12" s="9">
-        <v>60</v>
+        <v>10</v>
       </c>
       <c r="G12" s="1" t="s">
         <v>11</v>
       </c>
       <c r="H12" s="23">
-        <v>56</v>
+        <v>0</v>
       </c>
       <c r="I12" s="23">
+        <v>4</v>
+      </c>
+      <c r="J12" s="23">
+        <f t="shared" si="1"/>
         <v>10</v>
-      </c>
-      <c r="J12" s="23">
-        <v>4</v>
       </c>
     </row>
     <row r="13" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.25">
@@ -1127,31 +1133,30 @@
         <v>12</v>
       </c>
       <c r="B13" s="10">
-        <f t="shared" si="2"/>
-        <v>0.56989247311827962</v>
+        <v>0</v>
       </c>
       <c r="C13" s="10">
         <f t="shared" si="0"/>
-        <v>0.8833333333333333</v>
+        <v>0</v>
       </c>
       <c r="D13" s="11">
-        <f t="shared" si="1"/>
-        <v>0.69281045751633996</v>
+        <v>0</v>
       </c>
       <c r="E13" s="9">
-        <v>60</v>
+        <v>10</v>
       </c>
       <c r="G13" s="1" t="s">
         <v>12</v>
       </c>
       <c r="H13" s="23">
-        <v>53</v>
+        <v>0</v>
       </c>
       <c r="I13" s="23">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="J13" s="23">
-        <v>7</v>
+        <f t="shared" si="1"/>
+        <v>10</v>
       </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.2">
@@ -1160,15 +1165,15 @@
       </c>
       <c r="B14" s="15">
         <f>AVERAGE(B2:B13)</f>
-        <v>0.80951040611630942</v>
+        <v>0.31856952571238289</v>
       </c>
       <c r="C14" s="15">
-        <f t="shared" ref="C14:D14" si="3">AVERAGE(C2:C13)</f>
-        <v>0.77222222222222214</v>
+        <f t="shared" ref="C14:D14" si="4">AVERAGE(C2:C13)</f>
+        <v>0.39166666666666666</v>
       </c>
       <c r="D14" s="16">
-        <f t="shared" si="3"/>
-        <v>0.76549515408680102</v>
+        <f t="shared" si="4"/>
+        <v>0.3169581203479509</v>
       </c>
       <c r="E14" s="12"/>
     </row>
@@ -1178,15 +1183,15 @@
       </c>
       <c r="B15" s="18">
         <f>SUMPRODUCT(B2:B13,E2:E13)/SUM(E2:E13)</f>
-        <v>0.80951040611630953</v>
+        <v>0.31856952571238289</v>
       </c>
       <c r="C15" s="18">
         <f>SUMPRODUCT(C2:C13,E2:E13) / SUM(E2:E13)</f>
-        <v>0.77222222222222225</v>
+        <v>0.39166666666666666</v>
       </c>
       <c r="D15" s="19">
         <f>SUMPRODUCT(D2:D13,E2:E13) / SUM(E2:E13)</f>
-        <v>0.76549515408680102</v>
+        <v>0.31695812034795084</v>
       </c>
       <c r="E15" s="12"/>
     </row>
@@ -1203,7 +1208,7 @@
       </c>
       <c r="B18" s="7">
         <f>SUM(H2:H13)/(SUM(H2:H13)+SUM(J2:J13))</f>
-        <v>0.77222222222222225</v>
+        <v>0.39166666666666666</v>
       </c>
       <c r="C18" s="3"/>
       <c r="D18" s="3"/>
@@ -1215,7 +1220,7 @@
       </c>
       <c r="B19" s="7">
         <f>AVERAGE(D2:D13)</f>
-        <v>0.76549515408680102</v>
+        <v>0.3169581203479509</v>
       </c>
       <c r="C19" s="3"/>
       <c r="D19" s="3"/>
@@ -1227,7 +1232,7 @@
       </c>
       <c r="B20" s="7">
         <f>AVERAGE(B2:B13)</f>
-        <v>0.80951040611630942</v>
+        <v>0.31856952571238289</v>
       </c>
       <c r="C20" s="3"/>
       <c r="D20" s="3"/>
@@ -1239,7 +1244,7 @@
       </c>
       <c r="B21" s="7">
         <f>AVERAGE(C2:C13)</f>
-        <v>0.77222222222222214</v>
+        <v>0.39166666666666666</v>
       </c>
       <c r="C21" s="3"/>
       <c r="D21" s="3"/>
